--- a/config/fragments.xlsx
+++ b/config/fragments.xlsx
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>のカケラ名称</t>
+          <t>片断名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ナツミのカケラ</t>
+          <t>夏天的碎片</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ナツミ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#纳兹米#C0x55504D#</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>リコのカケラ</t>
+          <t>里子碎片</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リコ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#里科#C0x55504D#</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>モカのカケラ</t>
+          <t>摩卡碎片</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#モカ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#摩卡#C0x55504D#</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>グレイのカケラ</t>
+          <t>灰色的碎片</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#グレイ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#灰色#C0x55504D#</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>レイのカケラ</t>
+          <t>灵的碎片</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#レイ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#雷#C0x55504D#</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>フウカのカケラ</t>
+          <t>风歌的碎片</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#フウカ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#风歌#C0x55504D#</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>リクトのカケラ</t>
+          <t>陆斗的碎片</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リクト#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#陆地#C0x55504D#</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>サキのカケラ</t>
+          <t>先前的碎片</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#サキ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#萨琪#C0x55504D#</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>チヨのカケラ</t>
+          <t>千代的碎片</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#チヨ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#千代#C0x55504D#</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ルナのカケラ</t>
+          <t>露娜的碎片</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ルナ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#露娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>リサのカケラ</t>
+          <t>丽莎的碎片</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リサ#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#丽莎#C0x55504D#</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ミキのカケラ</t>
+          <t>三木片</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ミキ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#miki#C0x55504D#</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>リックのカケラ</t>
+          <t>里克的碎片</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リック#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#里克#C0x55504D#</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>スイのカケラ</t>
+          <t>西瓜碴儿</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#スイ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#西瓜#C0x55504D#</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#寶寶丁#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#宝石丁#C0x55504D#</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#超音蝠#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成到#C0xE77421#超音蝠#C0x55504D#上</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#走路草#C0x55504D#に合成できる</t>
+          <t>收集到%d个碎片就可以合成#C0xE77421#走道草#C0x55504D#</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>辉夜のカケラ</t>
+          <t>辉夜的碎片</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#辉夜#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#辉夜#C0x55504D#</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#喵喵#C0x55504D#に合成できる</t>
+          <t>可将%d个碎片合成为#C0xE77421#喵喵#C0x55504D#</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#可達鴨#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个可合成#C0xE77421#可达鸭#C0x55504D#</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>劳琳のカケラ</t>
+          <t>劳琳的碎片</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#劳琳#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#劳琳#C0x55504D#</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#卡蒂狗#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成为#C0xE77421#卡巴狗#C0x55504D#</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>セイラのカケラ</t>
+          <t>塞拉的碎片</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#セイラ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成成#C0xE77421#塞拉#C0x55504D#</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ロイのカケラ</t>
+          <t>罗伊的碎片</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ロイ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#罗伊#C0x55504D#</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>フランのカケラ</t>
+          <t>法郎的碎片</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#フラン#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#法郎#C0x55504D#</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>トウマのカケラ</t>
+          <t>马碴儿</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#トウマ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#托玛#C0x55504D#</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ユキのカケラ</t>
+          <t>雪花</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ユキ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#雪#C0x55504D#</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#大蔥鴨#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#大聪鸭#C0x55504D#</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#嘟嘟#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#嘟嘟#C0x55504D#</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>メグのカケラ</t>
+          <t>梅格碎片</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#メグ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#梅格#C0x55504D#</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#大舌貝#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#大舌贝#C0x55504D#</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>マコのカケラ</t>
+          <t>真子的碎片</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#マコ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#真可#C0x55504D#</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#大岩蛇#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#大岩蛇#C0x55504D#</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>マホのカケラ</t>
+          <t>真帆碎片</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#マホ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#真帆#C0x55504D#</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>千岛琳のカケラ</t>
+          <t>千岛琳的碎片</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#千岛琳#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#千岛琳#C0x55504D#</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>サクラのカケラ</t>
+          <t>樱花碴儿</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#サクラ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#樱花#C0x55504D#</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ベンのカケラ</t>
+          <t>瓣膜碎片</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ベン#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#本#C0x55504D#</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>白铃のカケラ</t>
+          <t>白铃的碎片</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#白铃#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#白铃#C0x55504D#</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>リックのカケラ</t>
+          <t>里克的碎片</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#小福蛋#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#小福蛋#C0x55504D#</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>丝琪のカケラ</t>
+          <t>丝琪的碎片</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#丝琪#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#丝琪#C0x55504D#</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>カイトのカケラ</t>
+          <t>风筝碎片</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#カイト#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#风筝#C0x55504D#</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ソラのカケラ</t>
+          <t>空的碎片</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ソラ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#天空#C0x55504D#</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>カリナのカケラ</t>
+          <t>卡琳娜的碎片</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#カリナ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#卡莉娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>アリサのカケラ</t>
+          <t>艾丽莎的碎片</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#アリサ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#艾丽莎#C0x55504D#</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#凱羅斯#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#卡洛斯#C0x55504D#</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Beeのカケラ</t>
+          <t>Bee的碎片</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#Bee#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#Bee#C0x55504D#</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#拉普拉斯#C0x55504D#に合成できる</t>
+          <t>收集到%d个碎片就可以合成#C0xE77421#拉普拉斯#C0x55504D#</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>リアのカケラ</t>
+          <t>后面的碎片</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リア#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#莉亚#C0x55504D#</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#化石翼龍#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#化石翼龙#C0x55504D#</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#小卡比獸#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#小卡比兽#C0x55504D#</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ハトリのカケラ</t>
+          <t>羽毛片</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ハトリ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#鸽子#C0x55504D#</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>ハヤトのカケラ</t>
+          <t>隼人的碎片</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ハヤト#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#隼人#C0x55504D#</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ロナ-メイドのカケラ</t>
+          <t>罗娜-女仆的碎片</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ロナ-メイド#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#萝娜女仆#C0x55504D#</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>イリアーナのカケラ</t>
+          <t>伊利雅娜的碎片</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#イリアーナ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#伊莉雅娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>カグラのカケラ</t>
+          <t>神乐碎片</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#カグラ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#神乐#C0x55504D#</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>テオスのカケラ</t>
+          <t>泰奥斯的碎片</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#テオス#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#泰奥斯#C0x55504D#</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>エリサのカケラ</t>
+          <t>艾丽莎的碎片</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#エリサ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#艾丽莎#C0x55504D#</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>カエデのカケラ</t>
+          <t>枫叶片</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#カエデ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#枫树#C0x55504D#</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ナナミのカケラ</t>
+          <t>七波碎片</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ナナミ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#奈奈美#C0x55504D#</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#波克比#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#波克比#C0x55504D#</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ナギサのカケラ</t>
+          <t>渚的碎片</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ナギサ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#渚#C0x55504D#</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>レイナのカケラ</t>
+          <t>蕾娜的碎片</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#レイナ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#蕾娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#夢妖#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#梦妖#C0x55504D#</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#天蠍#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#天蝎#C0x55504D#</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#赫拉克羅斯#C0x55504D#に合成できる</t>
+          <t>收集到%d个碎片就可以合成#C0xE77421#生辰八字#C0x55504D#</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>コトリのカケラ</t>
+          <t>小鸟碎片</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#コトリ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#小鸟#C0x55504D#</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>マリのカケラ</t>
+          <t>马里的碎片</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#マリ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#马里#C0x55504D#</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>イグナのカケラ</t>
+          <t>伊格纳碎片</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#イグナ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#伊格纳#C0x55504D#</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>キースのカケラ</t>
+          <t>凯斯的碎片</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#キース#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#基斯#C0x55504D#</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ミレイのカケラ</t>
+          <t>美丽的碎片</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ミレイ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#米蕾#C0x55504D#</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>スミレのカケラ</t>
+          <t>紫罗兰片</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#スミレ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#紫罗兰#C0x55504D#</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ナトリのカケラ</t>
+          <t>菜鸟的碎片</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ナトリ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#纳托利#C0x55504D#</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>ハナ-水着のカケラ</t>
+          <t>花-泳装碎片</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ハナ-水着#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#哈娜-泳装#C0x55504D#</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>メイのカケラ</t>
+          <t>名字的碎片</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#メイ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#咪咪#C0x55504D#</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ミホのカケラ</t>
+          <t>美穗碎片</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ミホ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#美穗#C0x55504D#</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>アンナのカケラ</t>
+          <t>安娜的碎片</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#アンナ#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#安娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ルミナのカケラ</t>
+          <t>鲁米娜的碎片</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ルミナ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#露米娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>モモのカケラ</t>
+          <t>桃子碴儿</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#モモ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#桃子#C0x55504D#</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>绯村のカケラ</t>
+          <t>绯村的碎片</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#绯村#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#绯村#C0x55504D#</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>シオンのカケラ</t>
+          <t>锡安的碎片</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#シオン#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#紫苑#C0x55504D#</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>ダリアのカケラ</t>
+          <t>大丽花碎片</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ダリア#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#大丽花#C0x55504D#</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#晃晃斑#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#晃晃斑#C0x55504D#</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#醜醜魚#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#丑丑鱼#C0x55504D#</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#怨影娃娃#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#怨影娃娃#C0x55504D#</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>カヨのカケラ</t>
+          <t>佳代的碎片</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#カヨ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#卡约#C0x55504D#</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>エリカのカケラ</t>
+          <t>艾莉卡碎片</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#エリカ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#艾莉卡#C0x55504D#</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#雪童子#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#雪童子#C0x55504D#</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>リゼルのカケラ</t>
+          <t>里瑟尔的碎片</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リゼル#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#里泽尔#C0x55504D#</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#寶貝龍#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#宝贝龙#C0x55504D#</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ユイナのカケラ</t>
+          <t>尤娜的碎片</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ユイナ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#尤娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#雷吉洛克#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#雷吉洛克#C0x55504D#</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#雷吉安娜#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#雷吉娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#雷吉斯奇魯#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#雷吉斯奇鲁#C0x55504D#</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#拉帝亞斯#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#拉帝亚斯#C0x55504D#</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#拉帝歐斯#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#拉帝欧斯#C0x55504D#</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>シエルのカケラ</t>
+          <t>夏尔的碎片</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#シエル#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成成#C0xE77421#夏尔#C0x55504D#</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#小火焰猴#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#小火焰猴#C0x55504D#</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#波加曼#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#波加曼#C0x55504D#</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>リアのカケラ</t>
+          <t>后面的碎片</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リア#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#莉亚#C0x55504D#</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>青屿のカケラ</t>
+          <t>青屿的碎片</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#青屿#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#青屿#C0x55504D#</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#利歐路#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#利欧路#C0x55504D#</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>罗兹のカケラ</t>
+          <t>罗兹之维拉</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#罗兹#C0x55504D#に合成できる</t>
+          <t>集齐%d个碎片即可合成于#C0xE77421#罗兹#C0x55504D#</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>ハルトのカケラ</t>
+          <t>春天的碎片</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ハルト#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#哈特#C0x55504D#</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#克雷色利亞#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#克莱色利亚#C0x55504D#</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#藤藤蛇#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#藤藤蛇#C0x55504D#</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>ナコのカケラ</t>
+          <t>菜子的碎片</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ナコ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#奈可#C0x55504D#</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#水水獺#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#水獭#C0x55504D#</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>ノエルのカケラ</t>
+          <t>诺埃尔碎片</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ノエル#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#诺埃尔#C0x55504D#</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#螺釘地鼠#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#螺钉地鼠#C0x55504D#</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>蕾娜のカケラ</t>
+          <t>蕾娜的碎片</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#蕾娜#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#蕾娜#C0x55504D#</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>エルのカケラ</t>
+          <t>艾尔的碎片</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#エル#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#艾尔#C0x55504D#</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>マキのカケラ</t>
+          <t>柴片</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#マキ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#卷轴#C0x55504D#</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#索羅亞#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#索罗亚#C0x55504D#</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#泡沫栗鼠#C0x55504D#に合成できる</t>
+          <t>集齐%d个碎片就能合成#C0xE77421#泡沫栗鼠#C0x55504D#</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#哥德寶寶#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#哥德宝贝#C0x55504D#</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>春野桃のカケラ</t>
+          <t>春野桃片</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#春野桃#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#春野桃#C0x55504D#</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>ミクのカケラ</t>
+          <t>未来的碎片</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ミク#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#未来#C0x55504D#</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#輕飄飄-雌#C0x55504D#に合成できる</t>
+          <t>收集到%d个碎片就可以合成#C0xE77421#轻飘-雌#C0x55504D#</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#輕飄飄-雄#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#轻飘-雄#C0x55504D#</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>洛奈のカケラ</t>
+          <t>洛奈的碎片</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#洛奈#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#洛奈#C0x55504D#</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#???#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个的话#C0xE77421#？？？可以合成#C0x55504D#</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>牙牙のカケラ</t>
+          <t>牙齿碎片</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#牙牙#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#獠牙#C0x55504D#</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>タクヤのカケラ</t>
+          <t>拓哉的碎片</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#タクヤ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#拓也#C0x55504D#</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>シンジのカケラ</t>
+          <t>信慈的碎片</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#シンジ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#真嗣#C0x55504D#</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#單首龍#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#单龙#C0x55504D#</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#燃燒蟲#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#燃烧虫#C0x55504D#</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#勾帕路翁#C0x55504D#に合成できる</t>
+          <t>只要收集到%d个碎片就可以合成#C0xE77421#勾同路翁#C0x55504D#</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#代拉基翁#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#代拉基翁#C0x55504D#</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#畢力吉翁#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#毕力吉翁#C0x55504D#</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#龍卷雲#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#龙卷云#C0x55504D#</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#雷電雲#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#雷电云#C0x55504D#</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#土地雲#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#土地云#C0x55504D#</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#凱路迪歐#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#凯路迪奥#C0x55504D#</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>アイのカケラ</t>
+          <t>爱的碎片</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#アイ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#艾#C0x55504D#</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ユウリのカケラ</t>
+          <t>有利的碎片</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ユウリ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#有利#C0x55504D#</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>レオのカケラ</t>
+          <t>里奥的碎片</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#レオ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#雷欧#C0x55504D#</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -13658,7 +13658,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>ノゾミのカケラ</t>
+          <t>希望的碎片</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ノゾミ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#希望#C0x55504D#</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>初音洛のカケラ</t>
+          <t>初音洛的碎片</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#初音洛#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#初音洛#C0x55504D#</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>シオンのカケラ</t>
+          <t>锡安的碎片</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#シオン#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#紫苑#C0x55504D#</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>泉纱羽のカケラ</t>
+          <t>泉纱羽的碎片</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#泉纱羽#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#泉纱羽#C0x55504D#</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>赫内思のカケラ</t>
+          <t>赫内思的碎片</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#赫内思#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#赫内思#C0x55504D#</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>梨花のカケラ</t>
+          <t>梨花碴儿</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#梨花#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#梨花#C0x55504D#</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ミミルのカケラ</t>
+          <t>米尔的碎片</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ミミル#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#密米尔#C0x55504D#</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>ヒナタのカケラ</t>
+          <t>雏田的碎片</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -14293,7 +14293,7 @@
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ヒナタ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#雏田#C0x55504D#</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>リンのカケラ</t>
+          <t>磷片</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リン#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#磷#C0x55504D#</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#嗡蝠#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成到#C0xE77421#嗡嗡#C0x55504D#上</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#木木梟#C0x55504D#に合成できる</t>
+          <t>收集到%d个碎片就可以合成#C0xE77421#木木枭#C0x55504D#</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#球球海獅#C0x55504D#に合成できる</t>
+          <t>收集到%d个碎片就可以合成#C0xE77421#球球海狮#C0x55504D#</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#好壞星#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#好坏星#C0x55504D#</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#甜竹竹#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#甜竹竹#C0x55504D#</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#毒貝比#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#毒贝比#C0x55504D#</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#小智版皮卡丘#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#小智版皮卡丘#C0x55504D#</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#雷吉奇卡斯#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#雷吉奇卡斯#C0x55504D#</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#達克萊伊#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#达克莱伊#C0x55504D#</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#謝米#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#谢米#C0x55504D#</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#蒂安希#C0x55504D#に合成できる</t>
+          <t>集齐%d个碎片就能合成#C0xE77421#蒂安希#C0x55504D#</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#洛奇亞#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#洛奇亚#C0x55504D#</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>ユウカのカケラ</t>
+          <t>有花碎片</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ユウカ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#有卡#C0x55504D#</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>マリンのカケラ</t>
+          <t>马林鱼片</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#マリン#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#马林#C0x55504D#</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#裂空座#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#裂空座#C0x55504D#</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>碧游のカケラ</t>
+          <t>碧游的碎片</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#碧游#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#碧游#C0x55504D#</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#美洛耶塔-歌聲#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#美洛耶塔-歌声#C0x55504D#</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#帝牙盧卡#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#帝牙卢卡#C0x55504D#</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>リチのカケラ</t>
+          <t>理智的碎片</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#リチ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#里奇#C0x55504D#</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>藤琳杏のカケラ</t>
+          <t>藤琳杏的碎片</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#藤琳杏#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#藤琳杏#C0x55504D#</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>珂莱茵のカケラ</t>
+          <t>珂莱茵的碎片</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#珂莱茵#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#珂莱茵#C0x55504D#</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#捷克羅姆#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#捷克罗姆#C0x55504D#</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="I173" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#酋雷姆#C0x55504D#に合成できる</t>
+          <t>收集到%d个碎片就可以合成成#C0xE77421#酋长雷姆#C0x55504D#</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#懲戒胡帕#C0x55504D#に合成できる</t>
+          <t>只要收集到%d个碎片就可以合成#C0xE77421#惩戒胡帕#C0x55504D#</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="I175" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#索爾迦雷歐#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#索尔迦雷欧#C0x55504D#</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#美錄坦#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#美录坦#C0x55504D#</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -16829,7 +16829,7 @@
       </c>
       <c r="I177" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#伊裴爾塔爾#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#伊裴尔塔尔#C0x55504D#</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -16919,7 +16919,7 @@
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#時拉比#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#时拉比#C0x55504D#</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="I179" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#蓋諾賽克特#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#盖诺赛克特#C0x55504D#</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#哲爾尼亞斯#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#哲尔尼亚斯#C0x55504D#</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -17159,7 +17159,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>???のカケラ</t>
+          <t>???碎片</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#捷拉奧拉#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#捷拉奥拉#C0x55504D#</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>紫エッグモンのカケラ</t>
+          <t>紫蛋兽碎片</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#紫エッグモン#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#紫蛋兽#C0x55504D#</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>黄エッグモンのカケラ</t>
+          <t>黄蛋门的碎片</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -17354,7 +17354,7 @@
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#黄エッグモン#C0x55504D#に合成できる。戦闘力は弱いがS仲間の星レベルアップ時に仲間の代わりに使用できる。</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#黄蛋兽#C0x55504D#。战斗力较弱，但S伙伴的星级提升时可以代替伙伴使用。</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>赤エッグモンのカケラ</t>
+          <t>红蛋兽的碎片</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="I185" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#赤エッグモン#C0x55504D#に合成できる。戦闘力は弱いがS+仲間の星レベルアップ時に仲間の代わりに使用できる。</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#红蛋兽#C0x55504D#。战斗力较弱，但S+伙伴的星级提升时可以代替伙伴使用。</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>果物缶詰のカケラ</t>
+          <t>水果罐头碎片</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#果物缶詰#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#水果罐头#C0x55504D#</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>制御盤のカケラ</t>
+          <t>控制盘的碎片</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -17604,7 +17604,7 @@
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#制御盤#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成成#C0xE77421#控制盘#C0x55504D#</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -17671,7 +17671,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>増幅器のカケラ</t>
+          <t>放大器碎片</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="I190" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#増幅器#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#放大器#C0x55504D#</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -17706,7 +17706,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -17758,7 +17758,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>王者の証のカケラ</t>
+          <t>王者之证的碎片</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="I191" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#王者の証#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#王者之证#C0x55504D#</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>ハーブのカケラ</t>
+          <t>香草片</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -17865,7 +17865,7 @@
       </c>
       <c r="I192" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ハーブ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#香草#C0x55504D#</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>てるてる坊主のカケラ</t>
+          <t>晴天娃娃的碎片</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="I193" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#てるてる坊主#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#晴天娃娃#C0x55504D#</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -17967,7 +17967,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>海の砂のカケラ</t>
+          <t>海中的沙子碎片</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#海の砂#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#海砂#C0x55504D#</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>スカーフのカケラ</t>
+          <t>围巾碎片</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -18126,7 +18126,7 @@
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#スカーフ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就可以合成#C0xE77421#围巾#C0x55504D#</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>呪いの札のカケラ</t>
+          <t>诅咒牌碎片</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#呪いの札#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#诅咒之牌#C0x55504D#</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>竜の牙のカケラ</t>
+          <t>龙牙碎片</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#竜の牙#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#龙之牙#C0x55504D#</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>鉄鉱石のカケラ</t>
+          <t>铁矿石碎片</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#鉄鉱石#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#铁矿石#C0x55504D#</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>黒帯のカケラ</t>
+          <t>黑带碎片</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#黒帯#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#黑带#C0x55504D#</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -18489,7 +18489,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>防護フィルムのカケラ</t>
+          <t>防护薄膜碎片</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#防護フィルム#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#防护膜#C0x55504D#</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>改造チップのカケラ</t>
+          <t>改造芯片碎片</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#改造チップ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#改造芯片#C0x55504D#</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -18663,7 +18663,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>魔力原石のカケラ</t>
+          <t>魔力原石碎片</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="I202" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#魔力原石#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#魔力原石#C0x55504D#</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -18750,7 +18750,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>奇妙な香水のカケラ</t>
+          <t>奇怪的香水碎片</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#奇妙な香水#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#奇妙的香水#C0x55504D#</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>ハートの雫のカケラ</t>
+          <t>心形水滴碎片</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ハートの雫#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#心之水滴#C0x55504D#</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>対戦通信機のカケラ</t>
+          <t>对战通信机的碎片</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="I205" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#対戦通信機#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#对战通信机#C0x55504D#</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>時空マスクのカケラ</t>
+          <t>时空面具碎片</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="I206" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#時空マスク#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#时空面具#C0x55504D#</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>永劫の剣のカケラ</t>
+          <t>永恒之剑的碎片</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -19170,7 +19170,7 @@
       </c>
       <c r="I207" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#永劫の剣#C0x55504D#に合成できる</t>
+          <t>集齐%d个碎片就能合成#C0xE77421#永劫之剑#C0x55504D#</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -19237,7 +19237,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>赤焔の爪のカケラ</t>
+          <t>红色火焰爪碎片</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#赤焔の爪#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#赤焰之爪#C0x55504D#</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -19324,7 +19324,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>不朽の盾のカケラ</t>
+          <t>不朽的盾牌碎片</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="I209" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#不朽の盾#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#不朽之盾#C0x55504D#</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>コアバンドのカケラ</t>
+          <t>核心乐队的碎片</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="I210" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#コアバンド#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#核心带#C0x55504D#</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -19498,7 +19498,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>アームギアのカケラ</t>
+          <t>机械臂的碎片</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#アームギア#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#机械臂#C0x55504D#</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>精霊の笛のカケラ</t>
+          <t>精灵之笛的碎片</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#精霊の笛#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#精灵之笛#C0x55504D#</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -19672,7 +19672,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>共鳴元素のカケラ</t>
+          <t>共振元素的碎片</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="I213" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#共鳴元素#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#共鸣元素#C0x55504D#</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>ブルーギアのカケラ</t>
+          <t>蓝色齿轮碎片</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ブルーギア#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#蓝色齿轮#C0x55504D#</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>シルスコープのカケラ</t>
+          <t>锡尔斯普克碎片</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -19866,7 +19866,7 @@
       </c>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#シルスコープ#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#希尔斯普#C0x55504D#</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>博士帽のカケラ</t>
+          <t>博士帽片</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="I216" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#博士帽#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#博士帽#C0x55504D#</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>宝石の腕輪のカケラ</t>
+          <t>宝石手镯碎片</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="I217" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#宝石の腕輪#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#宝石手镯#C0x55504D#</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -20107,7 +20107,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>サイバー眼鏡のカケラ</t>
+          <t>网络眼镜碎片</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="I218" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#サイバー眼鏡#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#网络眼镜#C0x55504D#</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -20142,7 +20142,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>ヘッドギアのカケラ</t>
+          <t>头饰碎片</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -20214,7 +20214,7 @@
       </c>
       <c r="I219" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ヘッドギア#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#头套#C0x55504D#</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -20281,7 +20281,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>超音デバイスのカケラ</t>
+          <t>超声波设备碎片</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="I220" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#超音デバイス#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#超音装置#C0x55504D#</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -20368,7 +20368,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>音波ディスクのカケラ</t>
+          <t>声波磁盘碎片</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="I221" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#音波ディスク#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#声波光盘#C0x55504D#</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>探索器のカケラ</t>
+          <t>搜索器碎片</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -20475,7 +20475,7 @@
       </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#探索器#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#搜索器#C0x55504D#</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>真実の鏡のカケラ</t>
+          <t>真理的镜子碎片</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#真実の鏡#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#真实之镜#C0x55504D#</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -20629,7 +20629,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>神秘の首飾りのカケラ</t>
+          <t>神秘项链碎片</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="I224" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#神秘の首飾り#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#神秘项链#C0x55504D#</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>銀装シールドのカケラ</t>
+          <t>银护盾碎片</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="I225" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#銀装シールド#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#银护盾#C0x55504D#</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>武士仮面のカケラ</t>
+          <t>武士面具的碎片</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="I226" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#武士仮面#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#武士假面#C0x55504D#</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>邪鬼仮面のカケラ</t>
+          <t>恶魔假面的碎片</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="I227" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#邪鬼仮面#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#恶魔假面#C0x55504D#</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -20925,7 +20925,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>シディアの花のカケラ</t>
+          <t>西迪亚花碎片</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#シディアの花#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#西迪亚之花#C0x55504D#</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -21064,7 +21064,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>ソール時砂のカケラ</t>
+          <t>鞋底沙子碎片</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#ソール時砂#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#索尔时砂#C0x55504D#</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>遺因スパイクのカケラ</t>
+          <t>遗因钉鞋的碎片</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="I230" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#遺因スパイク#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#遗因钉#C0x55504D#</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>神の王冠のカケラ</t>
+          <t>上帝的王冠碎片</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="I231" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#神の王冠#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就能合成#C0xE77421#神之王冠#C0x55504D#</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>青万能石のカケラ</t>
+          <t>蓝色万能石碎片</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="I233" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#青万能石#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#蓝万能石#C0x55504D#</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>紫万能石のカケラ</t>
+          <t>紫色万能石碎片</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#紫万能石#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#紫万能石#C0x55504D#</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>橙万能石のカケラ</t>
+          <t>橙万能石碎片</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="I235" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#橙万能石#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#橙万能石#C0x55504D#</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>探査機δ選定箱のカケラ</t>
+          <t>探测器δ选择箱的碎片</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="I236" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#探査機δ選定箱#C0x55504D#に合成できる</t>
+          <t>收集%d个碎片就能合成#C0xE77421#探测器δ选定箱#C0x55504D#</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -21696,7 +21696,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>紫·装備選定箱のカケラ</t>
+          <t>紫色装备选定箱碎片</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -21726,7 +21726,7 @@
       </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#紫·装備選定箱#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#紫色·装备选定箱#C0x55504D#</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -21746,7 +21746,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>橙ルーン抽選箱のカケラ</t>
+          <t>橙符文抽奖箱的碎片</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="I238" s="3" t="inlineStr">
         <is>
-          <t>欠片を%d個集めると#C0xE77421#橙ルーン抽選箱#C0x55504D#に合成できる</t>
+          <t>收集碎片%d个就可以合成#C0xE77421#橙符文抽奖箱#C0x55504D#</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>コレクションの価値は非常に高く、多くのことを積むことができます</t>
+          <t>收藏的价值非常高，可以堆积很多东西</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
